--- a/src/src/main/webapp/portal/uaa/userAccount/APM_UserAccount_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/APM_UserAccount_Template.xlsx
@@ -14,10 +14,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
   <si>
-    <t>所属集团</t>
+    <t>所属集团*</t>
   </si>
   <si>
-    <t>所属医院*</t>
+    <t>所属医院</t>
   </si>
   <si>
     <t>所属院区</t>
@@ -394,31 +394,31 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="4" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="4" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -3881,7 +3881,7 @@
     <col min="6" max="256" width="8.85156" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1">
+    <row r="1" ht="13.7" customHeight="1">
       <c r="A1" t="s" s="13">
         <v>15</v>
       </c>
@@ -3890,14 +3890,14 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" ht="13.65" customHeight="1">
+    <row r="2" ht="13.7" customHeight="1">
       <c r="A2" s="16"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
     </row>
-    <row r="3" ht="16" customHeight="1">
+    <row r="3" ht="15.95" customHeight="1">
       <c r="A3" t="s" s="17">
         <v>16</v>
       </c>
@@ -3906,7 +3906,7 @@
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
     </row>
-    <row r="4" ht="16" customHeight="1">
+    <row r="4" ht="15.95" customHeight="1">
       <c r="A4" t="s" s="17">
         <v>17</v>
       </c>
@@ -3915,7 +3915,7 @@
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
     </row>
-    <row r="5" ht="16" customHeight="1">
+    <row r="5" ht="15.95" customHeight="1">
       <c r="A5" t="s" s="17">
         <v>18</v>
       </c>
@@ -3924,7 +3924,7 @@
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
     </row>
-    <row r="6" ht="16" customHeight="1">
+    <row r="6" ht="15.95" customHeight="1">
       <c r="A6" t="s" s="17">
         <v>19</v>
       </c>
@@ -3933,7 +3933,7 @@
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
     </row>
-    <row r="7" ht="16" customHeight="1">
+    <row r="7" ht="15.95" customHeight="1">
       <c r="A7" t="s" s="17">
         <v>20</v>
       </c>
@@ -3942,7 +3942,7 @@
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
     </row>
-    <row r="8" ht="16" customHeight="1">
+    <row r="8" ht="15.95" customHeight="1">
       <c r="A8" t="s" s="17">
         <v>21</v>
       </c>
@@ -3951,7 +3951,7 @@
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
     </row>
-    <row r="9" ht="16" customHeight="1">
+    <row r="9" ht="15.95" customHeight="1">
       <c r="A9" t="s" s="17">
         <v>22</v>
       </c>
@@ -3960,14 +3960,14 @@
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
     </row>
-    <row r="10" ht="16" customHeight="1">
+    <row r="10" ht="15.95" customHeight="1">
       <c r="A10" s="19"/>
       <c r="B10" s="14"/>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
     </row>
-    <row r="11" ht="13.65" customHeight="1">
+    <row r="11" ht="13.7" customHeight="1">
       <c r="A11" t="s" s="20">
         <v>23</v>
       </c>
@@ -3983,7 +3983,7 @@
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
     </row>
-    <row r="13" ht="16" customHeight="1">
+    <row r="13" ht="15.95" customHeight="1">
       <c r="A13" t="s" s="17">
         <v>24</v>
       </c>
@@ -3992,7 +3992,7 @@
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
     </row>
-    <row r="14" ht="16" customHeight="1">
+    <row r="14" ht="15.95" customHeight="1">
       <c r="A14" t="s" s="17">
         <v>25</v>
       </c>
@@ -4001,7 +4001,7 @@
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
     </row>
-    <row r="15" ht="16" customHeight="1">
+    <row r="15" ht="15.95" customHeight="1">
       <c r="A15" t="s" s="17">
         <v>26</v>
       </c>
@@ -4010,7 +4010,7 @@
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
     </row>
-    <row r="16" ht="16" customHeight="1">
+    <row r="16" ht="15.95" customHeight="1">
       <c r="A16" t="s" s="17">
         <v>27</v>
       </c>
@@ -4019,7 +4019,7 @@
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
     </row>
-    <row r="17" ht="16" customHeight="1">
+    <row r="17" ht="15.95" customHeight="1">
       <c r="A17" t="s" s="17">
         <v>28</v>
       </c>
@@ -4028,7 +4028,7 @@
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
     </row>
-    <row r="18" ht="16" customHeight="1">
+    <row r="18" ht="15.95" customHeight="1">
       <c r="A18" t="s" s="17">
         <v>29</v>
       </c>
@@ -4037,7 +4037,7 @@
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
     </row>
-    <row r="19" ht="16" customHeight="1">
+    <row r="19" ht="15.95" customHeight="1">
       <c r="A19" t="s" s="17">
         <v>30</v>
       </c>
@@ -4046,7 +4046,7 @@
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
     </row>
-    <row r="20" ht="16" customHeight="1">
+    <row r="20" ht="15.95" customHeight="1">
       <c r="A20" t="s" s="17">
         <v>31</v>
       </c>
@@ -4055,7 +4055,7 @@
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
     </row>
-    <row r="21" ht="16" customHeight="1">
+    <row r="21" ht="15.95" customHeight="1">
       <c r="A21" t="s" s="17">
         <v>32</v>
       </c>
@@ -4075,8 +4075,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A11:A12"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A11:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>

--- a/src/src/main/webapp/portal/uaa/userAccount/APM_UserAccount_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/APM_UserAccount_Template.xlsx
@@ -1,29 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="19126"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212706711\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{EC298B00-2EC5-49B6-9B12-4FE43BFF2C35}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="45" windowWidth="15960" windowHeight="18075" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28360" windowHeight="10220"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
-  <si>
-    <t>所属集团*</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35">
+  <si>
+    <t>所属集团</t>
   </si>
   <si>
     <t>所属医院</t>
@@ -74,6 +68,27 @@
     <t>1.在datalist sheet中带有*标记的列为必填项。</t>
   </si>
   <si>
+    <t>2.“科室1”、“科室2”和“科室3”分别表示“科室层级1”、“科室层级2”和“科室层级3”</t>
+  </si>
+  <si>
+    <t>3.角色列需要输入以下角色名称，否则系统找不到相对应的名称，不导入该条数据</t>
+  </si>
+  <si>
+    <t>4.若角色中同时填入“仅报修权限账号”和其他角色，则只导入“仅报修权限账号”角色</t>
+  </si>
+  <si>
+    <t>5.多个角色用逗号分隔(不区分大小写)，多个角色中其中有一条角色名称输入有误，则不导入该条数据</t>
+  </si>
+  <si>
+    <t>6.从系统导出时，会带有UUID列，此列不可更改，系统会根据UUID更新相应字段内容</t>
+  </si>
+  <si>
+    <t>7.可见范围中，输入除本人所在科室以外的其他科室名称，可见多个科室用逗号分隔</t>
+  </si>
+  <si>
+    <t>8.可见范围只支持科室的设定，院区、医院等不支持</t>
+  </si>
+  <si>
     <t>角色名称</t>
   </si>
   <si>
@@ -105,68 +120,190 @@
   </si>
   <si>
     <t>设备调剂管理人员</t>
-  </si>
-  <si>
-    <t>2.“科室1”、“科室2”和“科室3”分别表示“科室层级1”、“科室层级2”和“科室层级3”</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.角色列需要输入以下角色名称，否则系统找不到相对应的名称，不导入该条数据</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.若角色中同时填入“仅报修权限账号”和其他角色，则只导入“仅报修权限账号”角色</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>5.多个角色用逗号分隔(不区分大小写)，多个角色中其中有一条角色名称输入有误，则不导入该条数据</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.从系统导出时，会带有UUID列，此列不可更改，系统会根据UUID更新相应字段内容</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>7.可见范围中，输入除本人所在科室以外的其他科室名称，可见多个科室用逗号分隔</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>8.可见范围只支持科室的设定，院区、医院等不支持</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -176,37 +313,208 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="10"/>
-        <bgColor auto="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
-        <bgColor auto="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="17">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -221,32 +529,27 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="11"/>
       </left>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -277,68 +580,376 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color indexed="11"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color indexed="11"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color indexed="11"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FF4D5D2C"/>
-      <rgbColor rgb="FFAAAAAA"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="004D5D2C"/>
+      <rgbColor rgb="00AAAAAA"/>
       <rgbColor rgb="000000FF"/>
       <rgbColor rgb="00FFFF00"/>
       <rgbColor rgb="00FF00FF"/>
@@ -396,9 +1007,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -604,8 +1212,6 @@
           <a:prstDash val="solid"/>
           <a:round/>
         </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
@@ -625,7 +1231,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -655,7 +1260,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -681,7 +1285,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -707,7 +1310,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -733,7 +1335,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -759,7 +1360,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -785,7 +1385,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -811,7 +1410,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -837,7 +1435,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -863,7 +1460,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -899,8 +1495,6 @@
           <a:prstDash val="solid"/>
           <a:round/>
         </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
@@ -920,7 +1514,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -946,7 +1539,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -972,7 +1564,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -998,7 +1589,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1024,7 +1614,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1050,7 +1639,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1076,7 +1664,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1102,7 +1689,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1128,7 +1714,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1154,7 +1739,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1187,8 +1771,6 @@
           <a:noFill/>
           <a:miter lim="400000"/>
         </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
@@ -1208,7 +1790,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1238,7 +1819,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1264,7 +1844,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1290,7 +1869,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1316,7 +1894,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1342,7 +1919,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1368,7 +1944,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1394,7 +1969,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1420,7 +1994,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1446,7 +2019,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
@@ -1473,320 +2045,319 @@
       </a:style>
     </a:txDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr/>
   <dimension ref="A1:IU1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85714285714286" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="13.42578125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="14.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.2857142857143" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7142857142857" style="1" customWidth="1"/>
+    <col min="3" max="4" width="13.4285714285714" style="1" customWidth="1"/>
+    <col min="5" max="6" width="14.2857142857143" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7142857142857" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.85714285714286" style="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
-    <col min="11" max="12" width="8.85546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="24.7109375" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.85714285714286" style="1" customWidth="1"/>
+    <col min="13" max="13" width="24.7142857142857" style="1" customWidth="1"/>
     <col min="14" max="14" width="30" style="1" customWidth="1"/>
-    <col min="15" max="15" width="32.7109375" style="1" customWidth="1"/>
-    <col min="16" max="255" width="8.85546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="32.7142857142857" style="1" customWidth="1"/>
+    <col min="16" max="255" width="8.85714285714286" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:255" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="30.75" customHeight="1" spans="1:255">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4"/>
-      <c r="AD1" s="4"/>
-      <c r="AE1" s="4"/>
-      <c r="AF1" s="4"/>
-      <c r="AG1" s="4"/>
-      <c r="AH1" s="4"/>
-      <c r="AI1" s="4"/>
-      <c r="AJ1" s="4"/>
-      <c r="AK1" s="4"/>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
-      <c r="AP1" s="4"/>
-      <c r="AQ1" s="4"/>
-      <c r="AR1" s="4"/>
-      <c r="AS1" s="4"/>
-      <c r="AT1" s="4"/>
-      <c r="AU1" s="4"/>
-      <c r="AV1" s="4"/>
-      <c r="AW1" s="4"/>
-      <c r="AX1" s="4"/>
-      <c r="AY1" s="4"/>
-      <c r="AZ1" s="4"/>
-      <c r="BA1" s="4"/>
-      <c r="BB1" s="4"/>
-      <c r="BC1" s="4"/>
-      <c r="BD1" s="4"/>
-      <c r="BE1" s="4"/>
-      <c r="BF1" s="4"/>
-      <c r="BG1" s="4"/>
-      <c r="BH1" s="4"/>
-      <c r="BI1" s="4"/>
-      <c r="BJ1" s="4"/>
-      <c r="BK1" s="4"/>
-      <c r="BL1" s="4"/>
-      <c r="BM1" s="4"/>
-      <c r="BN1" s="4"/>
-      <c r="BO1" s="4"/>
-      <c r="BP1" s="4"/>
-      <c r="BQ1" s="4"/>
-      <c r="BR1" s="4"/>
-      <c r="BS1" s="4"/>
-      <c r="BT1" s="4"/>
-      <c r="BU1" s="4"/>
-      <c r="BV1" s="4"/>
-      <c r="BW1" s="4"/>
-      <c r="BX1" s="4"/>
-      <c r="BY1" s="4"/>
-      <c r="BZ1" s="4"/>
-      <c r="CA1" s="4"/>
-      <c r="CB1" s="4"/>
-      <c r="CC1" s="4"/>
-      <c r="CD1" s="4"/>
-      <c r="CE1" s="4"/>
-      <c r="CF1" s="4"/>
-      <c r="CG1" s="4"/>
-      <c r="CH1" s="4"/>
-      <c r="CI1" s="4"/>
-      <c r="CJ1" s="4"/>
-      <c r="CK1" s="4"/>
-      <c r="CL1" s="4"/>
-      <c r="CM1" s="4"/>
-      <c r="CN1" s="4"/>
-      <c r="CO1" s="4"/>
-      <c r="CP1" s="4"/>
-      <c r="CQ1" s="4"/>
-      <c r="CR1" s="4"/>
-      <c r="CS1" s="4"/>
-      <c r="CT1" s="4"/>
-      <c r="CU1" s="4"/>
-      <c r="CV1" s="4"/>
-      <c r="CW1" s="4"/>
-      <c r="CX1" s="4"/>
-      <c r="CY1" s="4"/>
-      <c r="CZ1" s="4"/>
-      <c r="DA1" s="4"/>
-      <c r="DB1" s="4"/>
-      <c r="DC1" s="4"/>
-      <c r="DD1" s="4"/>
-      <c r="DE1" s="4"/>
-      <c r="DF1" s="4"/>
-      <c r="DG1" s="4"/>
-      <c r="DH1" s="4"/>
-      <c r="DI1" s="4"/>
-      <c r="DJ1" s="4"/>
-      <c r="DK1" s="4"/>
-      <c r="DL1" s="4"/>
-      <c r="DM1" s="4"/>
-      <c r="DN1" s="4"/>
-      <c r="DO1" s="4"/>
-      <c r="DP1" s="4"/>
-      <c r="DQ1" s="4"/>
-      <c r="DR1" s="4"/>
-      <c r="DS1" s="4"/>
-      <c r="DT1" s="4"/>
-      <c r="DU1" s="4"/>
-      <c r="DV1" s="4"/>
-      <c r="DW1" s="4"/>
-      <c r="DX1" s="4"/>
-      <c r="DY1" s="4"/>
-      <c r="DZ1" s="4"/>
-      <c r="EA1" s="4"/>
-      <c r="EB1" s="4"/>
-      <c r="EC1" s="4"/>
-      <c r="ED1" s="4"/>
-      <c r="EE1" s="4"/>
-      <c r="EF1" s="4"/>
-      <c r="EG1" s="4"/>
-      <c r="EH1" s="4"/>
-      <c r="EI1" s="4"/>
-      <c r="EJ1" s="4"/>
-      <c r="EK1" s="4"/>
-      <c r="EL1" s="4"/>
-      <c r="EM1" s="4"/>
-      <c r="EN1" s="4"/>
-      <c r="EO1" s="4"/>
-      <c r="EP1" s="4"/>
-      <c r="EQ1" s="4"/>
-      <c r="ER1" s="4"/>
-      <c r="ES1" s="4"/>
-      <c r="ET1" s="4"/>
-      <c r="EU1" s="4"/>
-      <c r="EV1" s="4"/>
-      <c r="EW1" s="4"/>
-      <c r="EX1" s="4"/>
-      <c r="EY1" s="4"/>
-      <c r="EZ1" s="4"/>
-      <c r="FA1" s="4"/>
-      <c r="FB1" s="4"/>
-      <c r="FC1" s="4"/>
-      <c r="FD1" s="4"/>
-      <c r="FE1" s="4"/>
-      <c r="FF1" s="4"/>
-      <c r="FG1" s="4"/>
-      <c r="FH1" s="4"/>
-      <c r="FI1" s="4"/>
-      <c r="FJ1" s="4"/>
-      <c r="FK1" s="4"/>
-      <c r="FL1" s="4"/>
-      <c r="FM1" s="4"/>
-      <c r="FN1" s="4"/>
-      <c r="FO1" s="4"/>
-      <c r="FP1" s="4"/>
-      <c r="FQ1" s="4"/>
-      <c r="FR1" s="4"/>
-      <c r="FS1" s="4"/>
-      <c r="FT1" s="4"/>
-      <c r="FU1" s="4"/>
-      <c r="FV1" s="4"/>
-      <c r="FW1" s="4"/>
-      <c r="FX1" s="4"/>
-      <c r="FY1" s="4"/>
-      <c r="FZ1" s="4"/>
-      <c r="GA1" s="4"/>
-      <c r="GB1" s="4"/>
-      <c r="GC1" s="4"/>
-      <c r="GD1" s="4"/>
-      <c r="GE1" s="4"/>
-      <c r="GF1" s="4"/>
-      <c r="GG1" s="4"/>
-      <c r="GH1" s="4"/>
-      <c r="GI1" s="4"/>
-      <c r="GJ1" s="4"/>
-      <c r="GK1" s="4"/>
-      <c r="GL1" s="4"/>
-      <c r="GM1" s="4"/>
-      <c r="GN1" s="4"/>
-      <c r="GO1" s="4"/>
-      <c r="GP1" s="4"/>
-      <c r="GQ1" s="4"/>
-      <c r="GR1" s="4"/>
-      <c r="GS1" s="4"/>
-      <c r="GT1" s="4"/>
-      <c r="GU1" s="4"/>
-      <c r="GV1" s="4"/>
-      <c r="GW1" s="4"/>
-      <c r="GX1" s="4"/>
-      <c r="GY1" s="4"/>
-      <c r="GZ1" s="4"/>
-      <c r="HA1" s="4"/>
-      <c r="HB1" s="4"/>
-      <c r="HC1" s="4"/>
-      <c r="HD1" s="4"/>
-      <c r="HE1" s="4"/>
-      <c r="HF1" s="4"/>
-      <c r="HG1" s="4"/>
-      <c r="HH1" s="4"/>
-      <c r="HI1" s="4"/>
-      <c r="HJ1" s="4"/>
-      <c r="HK1" s="4"/>
-      <c r="HL1" s="4"/>
-      <c r="HM1" s="4"/>
-      <c r="HN1" s="4"/>
-      <c r="HO1" s="4"/>
-      <c r="HP1" s="4"/>
-      <c r="HQ1" s="4"/>
-      <c r="HR1" s="4"/>
-      <c r="HS1" s="4"/>
-      <c r="HT1" s="4"/>
-      <c r="HU1" s="4"/>
-      <c r="HV1" s="4"/>
-      <c r="HW1" s="4"/>
-      <c r="HX1" s="4"/>
-      <c r="HY1" s="4"/>
-      <c r="HZ1" s="4"/>
-      <c r="IA1" s="4"/>
-      <c r="IB1" s="4"/>
-      <c r="IC1" s="4"/>
-      <c r="ID1" s="4"/>
-      <c r="IE1" s="4"/>
-      <c r="IF1" s="4"/>
-      <c r="IG1" s="4"/>
-      <c r="IH1" s="4"/>
-      <c r="II1" s="4"/>
-      <c r="IJ1" s="4"/>
-      <c r="IK1" s="4"/>
-      <c r="IL1" s="4"/>
-      <c r="IM1" s="4"/>
-      <c r="IN1" s="4"/>
-      <c r="IO1" s="4"/>
-      <c r="IP1" s="4"/>
-      <c r="IQ1" s="4"/>
-      <c r="IR1" s="4"/>
-      <c r="IS1" s="4"/>
-      <c r="IT1" s="4"/>
-      <c r="IU1" s="5"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="11"/>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
+      <c r="AD1" s="11"/>
+      <c r="AE1" s="11"/>
+      <c r="AF1" s="11"/>
+      <c r="AG1" s="11"/>
+      <c r="AH1" s="11"/>
+      <c r="AI1" s="11"/>
+      <c r="AJ1" s="11"/>
+      <c r="AK1" s="11"/>
+      <c r="AL1" s="11"/>
+      <c r="AM1" s="11"/>
+      <c r="AN1" s="11"/>
+      <c r="AO1" s="11"/>
+      <c r="AP1" s="11"/>
+      <c r="AQ1" s="11"/>
+      <c r="AR1" s="11"/>
+      <c r="AS1" s="11"/>
+      <c r="AT1" s="11"/>
+      <c r="AU1" s="11"/>
+      <c r="AV1" s="11"/>
+      <c r="AW1" s="11"/>
+      <c r="AX1" s="11"/>
+      <c r="AY1" s="11"/>
+      <c r="AZ1" s="11"/>
+      <c r="BA1" s="11"/>
+      <c r="BB1" s="11"/>
+      <c r="BC1" s="11"/>
+      <c r="BD1" s="11"/>
+      <c r="BE1" s="11"/>
+      <c r="BF1" s="11"/>
+      <c r="BG1" s="11"/>
+      <c r="BH1" s="11"/>
+      <c r="BI1" s="11"/>
+      <c r="BJ1" s="11"/>
+      <c r="BK1" s="11"/>
+      <c r="BL1" s="11"/>
+      <c r="BM1" s="11"/>
+      <c r="BN1" s="11"/>
+      <c r="BO1" s="11"/>
+      <c r="BP1" s="11"/>
+      <c r="BQ1" s="11"/>
+      <c r="BR1" s="11"/>
+      <c r="BS1" s="11"/>
+      <c r="BT1" s="11"/>
+      <c r="BU1" s="11"/>
+      <c r="BV1" s="11"/>
+      <c r="BW1" s="11"/>
+      <c r="BX1" s="11"/>
+      <c r="BY1" s="11"/>
+      <c r="BZ1" s="11"/>
+      <c r="CA1" s="11"/>
+      <c r="CB1" s="11"/>
+      <c r="CC1" s="11"/>
+      <c r="CD1" s="11"/>
+      <c r="CE1" s="11"/>
+      <c r="CF1" s="11"/>
+      <c r="CG1" s="11"/>
+      <c r="CH1" s="11"/>
+      <c r="CI1" s="11"/>
+      <c r="CJ1" s="11"/>
+      <c r="CK1" s="11"/>
+      <c r="CL1" s="11"/>
+      <c r="CM1" s="11"/>
+      <c r="CN1" s="11"/>
+      <c r="CO1" s="11"/>
+      <c r="CP1" s="11"/>
+      <c r="CQ1" s="11"/>
+      <c r="CR1" s="11"/>
+      <c r="CS1" s="11"/>
+      <c r="CT1" s="11"/>
+      <c r="CU1" s="11"/>
+      <c r="CV1" s="11"/>
+      <c r="CW1" s="11"/>
+      <c r="CX1" s="11"/>
+      <c r="CY1" s="11"/>
+      <c r="CZ1" s="11"/>
+      <c r="DA1" s="11"/>
+      <c r="DB1" s="11"/>
+      <c r="DC1" s="11"/>
+      <c r="DD1" s="11"/>
+      <c r="DE1" s="11"/>
+      <c r="DF1" s="11"/>
+      <c r="DG1" s="11"/>
+      <c r="DH1" s="11"/>
+      <c r="DI1" s="11"/>
+      <c r="DJ1" s="11"/>
+      <c r="DK1" s="11"/>
+      <c r="DL1" s="11"/>
+      <c r="DM1" s="11"/>
+      <c r="DN1" s="11"/>
+      <c r="DO1" s="11"/>
+      <c r="DP1" s="11"/>
+      <c r="DQ1" s="11"/>
+      <c r="DR1" s="11"/>
+      <c r="DS1" s="11"/>
+      <c r="DT1" s="11"/>
+      <c r="DU1" s="11"/>
+      <c r="DV1" s="11"/>
+      <c r="DW1" s="11"/>
+      <c r="DX1" s="11"/>
+      <c r="DY1" s="11"/>
+      <c r="DZ1" s="11"/>
+      <c r="EA1" s="11"/>
+      <c r="EB1" s="11"/>
+      <c r="EC1" s="11"/>
+      <c r="ED1" s="11"/>
+      <c r="EE1" s="11"/>
+      <c r="EF1" s="11"/>
+      <c r="EG1" s="11"/>
+      <c r="EH1" s="11"/>
+      <c r="EI1" s="11"/>
+      <c r="EJ1" s="11"/>
+      <c r="EK1" s="11"/>
+      <c r="EL1" s="11"/>
+      <c r="EM1" s="11"/>
+      <c r="EN1" s="11"/>
+      <c r="EO1" s="11"/>
+      <c r="EP1" s="11"/>
+      <c r="EQ1" s="11"/>
+      <c r="ER1" s="11"/>
+      <c r="ES1" s="11"/>
+      <c r="ET1" s="11"/>
+      <c r="EU1" s="11"/>
+      <c r="EV1" s="11"/>
+      <c r="EW1" s="11"/>
+      <c r="EX1" s="11"/>
+      <c r="EY1" s="11"/>
+      <c r="EZ1" s="11"/>
+      <c r="FA1" s="11"/>
+      <c r="FB1" s="11"/>
+      <c r="FC1" s="11"/>
+      <c r="FD1" s="11"/>
+      <c r="FE1" s="11"/>
+      <c r="FF1" s="11"/>
+      <c r="FG1" s="11"/>
+      <c r="FH1" s="11"/>
+      <c r="FI1" s="11"/>
+      <c r="FJ1" s="11"/>
+      <c r="FK1" s="11"/>
+      <c r="FL1" s="11"/>
+      <c r="FM1" s="11"/>
+      <c r="FN1" s="11"/>
+      <c r="FO1" s="11"/>
+      <c r="FP1" s="11"/>
+      <c r="FQ1" s="11"/>
+      <c r="FR1" s="11"/>
+      <c r="FS1" s="11"/>
+      <c r="FT1" s="11"/>
+      <c r="FU1" s="11"/>
+      <c r="FV1" s="11"/>
+      <c r="FW1" s="11"/>
+      <c r="FX1" s="11"/>
+      <c r="FY1" s="11"/>
+      <c r="FZ1" s="11"/>
+      <c r="GA1" s="11"/>
+      <c r="GB1" s="11"/>
+      <c r="GC1" s="11"/>
+      <c r="GD1" s="11"/>
+      <c r="GE1" s="11"/>
+      <c r="GF1" s="11"/>
+      <c r="GG1" s="11"/>
+      <c r="GH1" s="11"/>
+      <c r="GI1" s="11"/>
+      <c r="GJ1" s="11"/>
+      <c r="GK1" s="11"/>
+      <c r="GL1" s="11"/>
+      <c r="GM1" s="11"/>
+      <c r="GN1" s="11"/>
+      <c r="GO1" s="11"/>
+      <c r="GP1" s="11"/>
+      <c r="GQ1" s="11"/>
+      <c r="GR1" s="11"/>
+      <c r="GS1" s="11"/>
+      <c r="GT1" s="11"/>
+      <c r="GU1" s="11"/>
+      <c r="GV1" s="11"/>
+      <c r="GW1" s="11"/>
+      <c r="GX1" s="11"/>
+      <c r="GY1" s="11"/>
+      <c r="GZ1" s="11"/>
+      <c r="HA1" s="11"/>
+      <c r="HB1" s="11"/>
+      <c r="HC1" s="11"/>
+      <c r="HD1" s="11"/>
+      <c r="HE1" s="11"/>
+      <c r="HF1" s="11"/>
+      <c r="HG1" s="11"/>
+      <c r="HH1" s="11"/>
+      <c r="HI1" s="11"/>
+      <c r="HJ1" s="11"/>
+      <c r="HK1" s="11"/>
+      <c r="HL1" s="11"/>
+      <c r="HM1" s="11"/>
+      <c r="HN1" s="11"/>
+      <c r="HO1" s="11"/>
+      <c r="HP1" s="11"/>
+      <c r="HQ1" s="11"/>
+      <c r="HR1" s="11"/>
+      <c r="HS1" s="11"/>
+      <c r="HT1" s="11"/>
+      <c r="HU1" s="11"/>
+      <c r="HV1" s="11"/>
+      <c r="HW1" s="11"/>
+      <c r="HX1" s="11"/>
+      <c r="HY1" s="11"/>
+      <c r="HZ1" s="11"/>
+      <c r="IA1" s="11"/>
+      <c r="IB1" s="11"/>
+      <c r="IC1" s="11"/>
+      <c r="ID1" s="11"/>
+      <c r="IE1" s="11"/>
+      <c r="IF1" s="11"/>
+      <c r="IG1" s="11"/>
+      <c r="IH1" s="11"/>
+      <c r="II1" s="11"/>
+      <c r="IJ1" s="11"/>
+      <c r="IK1" s="11"/>
+      <c r="IL1" s="11"/>
+      <c r="IM1" s="11"/>
+      <c r="IN1" s="11"/>
+      <c r="IO1" s="11"/>
+      <c r="IP1" s="11"/>
+      <c r="IQ1" s="11"/>
+      <c r="IR1" s="11"/>
+      <c r="IS1" s="11"/>
+      <c r="IT1" s="11"/>
+      <c r="IU1" s="12"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -1794,24 +2365,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr/>
   <dimension ref="A1:IR23"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85714285714286" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="108.7109375" style="6" customWidth="1"/>
-    <col min="2" max="252" width="8.85546875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="108.714285714286" style="1" customWidth="1"/>
+    <col min="2" max="252" width="8.85714285714286" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:252" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+    <row r="1" ht="13.7" customHeight="1" spans="1:1">
+      <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:252" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="12"/>
+    <row r="2" ht="13.7" customHeight="1" spans="1:1">
+      <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:252" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+    <row r="3" ht="15.95" customHeight="1" spans="1:252">
+      <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
       <c r="IO3"/>
@@ -1819,142 +2391,141 @@
       <c r="IQ3"/>
       <c r="IR3"/>
     </row>
-    <row r="4" spans="1:252" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
-        <v>28</v>
+    <row r="4" ht="15.95" customHeight="1" spans="1:252">
+      <c r="A4" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="IO4"/>
       <c r="IP4"/>
       <c r="IQ4"/>
       <c r="IR4"/>
     </row>
-    <row r="5" spans="1:252" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
-        <v>29</v>
+    <row r="5" ht="15.95" customHeight="1" spans="1:252">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="IO5"/>
       <c r="IP5"/>
       <c r="IQ5"/>
       <c r="IR5"/>
     </row>
-    <row r="6" spans="1:252" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
-        <v>30</v>
+    <row r="6" ht="15.95" customHeight="1" spans="1:252">
+      <c r="A6" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="IO6"/>
       <c r="IP6"/>
       <c r="IQ6"/>
       <c r="IR6"/>
     </row>
-    <row r="7" spans="1:252" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
-        <v>31</v>
+    <row r="7" ht="15.95" customHeight="1" spans="1:252">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="IO7"/>
       <c r="IP7"/>
       <c r="IQ7"/>
       <c r="IR7"/>
     </row>
-    <row r="8" spans="1:252" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
-        <v>32</v>
+    <row r="8" ht="15.95" customHeight="1" spans="1:252">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="IO8"/>
       <c r="IP8"/>
       <c r="IQ8"/>
       <c r="IR8"/>
     </row>
-    <row r="9" spans="1:252" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
-        <v>33</v>
+    <row r="9" ht="15.95" customHeight="1" spans="1:252">
+      <c r="A9" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="IO9"/>
       <c r="IP9"/>
       <c r="IQ9"/>
       <c r="IR9"/>
     </row>
-    <row r="10" spans="1:252" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
-        <v>34</v>
+    <row r="10" ht="15.95" customHeight="1" spans="1:252">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="IO10"/>
       <c r="IP10"/>
       <c r="IQ10"/>
       <c r="IR10"/>
     </row>
-    <row r="11" spans="1:252" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="13"/>
+    <row r="11" ht="15.95" customHeight="1" spans="1:252">
+      <c r="A11" s="5"/>
       <c r="IO11"/>
       <c r="IP11"/>
       <c r="IQ11"/>
       <c r="IR11"/>
     </row>
-    <row r="12" spans="1:252" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
-        <v>17</v>
+    <row r="12" ht="13.7" customHeight="1" spans="1:1">
+      <c r="A12" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:252" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="8"/>
+    <row r="13" ht="12" customHeight="1" spans="1:1">
+      <c r="A13" s="7"/>
     </row>
-    <row r="14" spans="1:252" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
-        <v>18</v>
+    <row r="14" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A14" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:252" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>19</v>
+    <row r="15" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A15" s="8" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:252" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
-        <v>20</v>
+    <row r="16" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A16" s="8" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
-        <v>21</v>
+    <row r="17" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A17" s="8" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
-        <v>22</v>
+    <row r="18" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A18" s="8" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
-        <v>23</v>
+    <row r="19" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A19" s="8" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
-        <v>24</v>
+    <row r="20" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A20" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
-        <v>25</v>
+    <row r="21" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A21" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="11" t="s">
-        <v>26</v>
+    <row r="22" ht="15.95" customHeight="1" spans="1:1">
+      <c r="A22" s="8" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="11" t="s">
-        <v>27</v>
+    <row r="23" ht="13.5" customHeight="1" spans="1:1">
+      <c r="A23" s="8" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A1:A2"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/src/src/main/webapp/portal/uaa/userAccount/APM_UserAccount_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/APM_UserAccount_Template.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10610"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qtang/Desktop/APM/Git/hc-apm-web/src/src/main/webapp/portal/uaa/userAccount/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{98FDF696-3C92-4345-9205-AC46F6727823}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28360" windowHeight="10220"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="28360" windowHeight="10220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
@@ -15,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>所属集团</t>
   </si>
@@ -120,19 +126,16 @@
   </si>
   <si>
     <t>设备调剂管理人员</t>
+  </si>
+  <si>
+    <t>初始密码</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -151,159 +154,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -322,194 +174,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="17">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -613,269 +279,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -883,58 +295,23 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
-    <cellStyle name="Total" xfId="25" builtinId="25"/>
-    <cellStyle name="Output" xfId="26" builtinId="21"/>
-    <cellStyle name="Currency" xfId="27" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
-    <cellStyle name="Note" xfId="29" builtinId="10"/>
-    <cellStyle name="Input" xfId="30" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
-    <cellStyle name="Good" xfId="33" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
-    <cellStyle name="Title" xfId="39" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
-    <cellStyle name="Comma" xfId="44" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
-    <cellStyle name="Percent" xfId="47" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
@@ -1007,6 +384,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2045,319 +1425,322 @@
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
-  <dimension ref="A1:IU1"/>
-  <sheetFormatPr defaultColWidth="8.85714285714286" defaultRowHeight="12.75" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:IV1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.2857142857143" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7142857142857" style="1" customWidth="1"/>
-    <col min="3" max="4" width="13.4285714285714" style="1" customWidth="1"/>
-    <col min="5" max="6" width="14.2857142857143" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7142857142857" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.85714285714286" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="13.5" style="1" customWidth="1"/>
+    <col min="5" max="6" width="14.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.83203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
-    <col min="11" max="12" width="8.85714285714286" style="1" customWidth="1"/>
-    <col min="13" max="13" width="24.7142857142857" style="1" customWidth="1"/>
-    <col min="14" max="14" width="30" style="1" customWidth="1"/>
-    <col min="15" max="15" width="32.7142857142857" style="1" customWidth="1"/>
-    <col min="16" max="255" width="8.85714285714286" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.83203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="24.6640625" style="1" customWidth="1"/>
+    <col min="14" max="15" width="30" style="1" customWidth="1"/>
+    <col min="16" max="16" width="32.6640625" style="1" customWidth="1"/>
+    <col min="17" max="256" width="8.83203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30.75" customHeight="1" spans="1:255">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:256" ht="30.75" customHeight="1">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="V1" s="11"/>
-      <c r="W1" s="11"/>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="11"/>
-      <c r="AA1" s="11"/>
-      <c r="AB1" s="11"/>
-      <c r="AC1" s="11"/>
-      <c r="AD1" s="11"/>
-      <c r="AE1" s="11"/>
-      <c r="AF1" s="11"/>
-      <c r="AG1" s="11"/>
-      <c r="AH1" s="11"/>
-      <c r="AI1" s="11"/>
-      <c r="AJ1" s="11"/>
-      <c r="AK1" s="11"/>
-      <c r="AL1" s="11"/>
-      <c r="AM1" s="11"/>
-      <c r="AN1" s="11"/>
-      <c r="AO1" s="11"/>
-      <c r="AP1" s="11"/>
-      <c r="AQ1" s="11"/>
-      <c r="AR1" s="11"/>
-      <c r="AS1" s="11"/>
-      <c r="AT1" s="11"/>
-      <c r="AU1" s="11"/>
-      <c r="AV1" s="11"/>
-      <c r="AW1" s="11"/>
-      <c r="AX1" s="11"/>
-      <c r="AY1" s="11"/>
-      <c r="AZ1" s="11"/>
-      <c r="BA1" s="11"/>
-      <c r="BB1" s="11"/>
-      <c r="BC1" s="11"/>
-      <c r="BD1" s="11"/>
-      <c r="BE1" s="11"/>
-      <c r="BF1" s="11"/>
-      <c r="BG1" s="11"/>
-      <c r="BH1" s="11"/>
-      <c r="BI1" s="11"/>
-      <c r="BJ1" s="11"/>
-      <c r="BK1" s="11"/>
-      <c r="BL1" s="11"/>
-      <c r="BM1" s="11"/>
-      <c r="BN1" s="11"/>
-      <c r="BO1" s="11"/>
-      <c r="BP1" s="11"/>
-      <c r="BQ1" s="11"/>
-      <c r="BR1" s="11"/>
-      <c r="BS1" s="11"/>
-      <c r="BT1" s="11"/>
-      <c r="BU1" s="11"/>
-      <c r="BV1" s="11"/>
-      <c r="BW1" s="11"/>
-      <c r="BX1" s="11"/>
-      <c r="BY1" s="11"/>
-      <c r="BZ1" s="11"/>
-      <c r="CA1" s="11"/>
-      <c r="CB1" s="11"/>
-      <c r="CC1" s="11"/>
-      <c r="CD1" s="11"/>
-      <c r="CE1" s="11"/>
-      <c r="CF1" s="11"/>
-      <c r="CG1" s="11"/>
-      <c r="CH1" s="11"/>
-      <c r="CI1" s="11"/>
-      <c r="CJ1" s="11"/>
-      <c r="CK1" s="11"/>
-      <c r="CL1" s="11"/>
-      <c r="CM1" s="11"/>
-      <c r="CN1" s="11"/>
-      <c r="CO1" s="11"/>
-      <c r="CP1" s="11"/>
-      <c r="CQ1" s="11"/>
-      <c r="CR1" s="11"/>
-      <c r="CS1" s="11"/>
-      <c r="CT1" s="11"/>
-      <c r="CU1" s="11"/>
-      <c r="CV1" s="11"/>
-      <c r="CW1" s="11"/>
-      <c r="CX1" s="11"/>
-      <c r="CY1" s="11"/>
-      <c r="CZ1" s="11"/>
-      <c r="DA1" s="11"/>
-      <c r="DB1" s="11"/>
-      <c r="DC1" s="11"/>
-      <c r="DD1" s="11"/>
-      <c r="DE1" s="11"/>
-      <c r="DF1" s="11"/>
-      <c r="DG1" s="11"/>
-      <c r="DH1" s="11"/>
-      <c r="DI1" s="11"/>
-      <c r="DJ1" s="11"/>
-      <c r="DK1" s="11"/>
-      <c r="DL1" s="11"/>
-      <c r="DM1" s="11"/>
-      <c r="DN1" s="11"/>
-      <c r="DO1" s="11"/>
-      <c r="DP1" s="11"/>
-      <c r="DQ1" s="11"/>
-      <c r="DR1" s="11"/>
-      <c r="DS1" s="11"/>
-      <c r="DT1" s="11"/>
-      <c r="DU1" s="11"/>
-      <c r="DV1" s="11"/>
-      <c r="DW1" s="11"/>
-      <c r="DX1" s="11"/>
-      <c r="DY1" s="11"/>
-      <c r="DZ1" s="11"/>
-      <c r="EA1" s="11"/>
-      <c r="EB1" s="11"/>
-      <c r="EC1" s="11"/>
-      <c r="ED1" s="11"/>
-      <c r="EE1" s="11"/>
-      <c r="EF1" s="11"/>
-      <c r="EG1" s="11"/>
-      <c r="EH1" s="11"/>
-      <c r="EI1" s="11"/>
-      <c r="EJ1" s="11"/>
-      <c r="EK1" s="11"/>
-      <c r="EL1" s="11"/>
-      <c r="EM1" s="11"/>
-      <c r="EN1" s="11"/>
-      <c r="EO1" s="11"/>
-      <c r="EP1" s="11"/>
-      <c r="EQ1" s="11"/>
-      <c r="ER1" s="11"/>
-      <c r="ES1" s="11"/>
-      <c r="ET1" s="11"/>
-      <c r="EU1" s="11"/>
-      <c r="EV1" s="11"/>
-      <c r="EW1" s="11"/>
-      <c r="EX1" s="11"/>
-      <c r="EY1" s="11"/>
-      <c r="EZ1" s="11"/>
-      <c r="FA1" s="11"/>
-      <c r="FB1" s="11"/>
-      <c r="FC1" s="11"/>
-      <c r="FD1" s="11"/>
-      <c r="FE1" s="11"/>
-      <c r="FF1" s="11"/>
-      <c r="FG1" s="11"/>
-      <c r="FH1" s="11"/>
-      <c r="FI1" s="11"/>
-      <c r="FJ1" s="11"/>
-      <c r="FK1" s="11"/>
-      <c r="FL1" s="11"/>
-      <c r="FM1" s="11"/>
-      <c r="FN1" s="11"/>
-      <c r="FO1" s="11"/>
-      <c r="FP1" s="11"/>
-      <c r="FQ1" s="11"/>
-      <c r="FR1" s="11"/>
-      <c r="FS1" s="11"/>
-      <c r="FT1" s="11"/>
-      <c r="FU1" s="11"/>
-      <c r="FV1" s="11"/>
-      <c r="FW1" s="11"/>
-      <c r="FX1" s="11"/>
-      <c r="FY1" s="11"/>
-      <c r="FZ1" s="11"/>
-      <c r="GA1" s="11"/>
-      <c r="GB1" s="11"/>
-      <c r="GC1" s="11"/>
-      <c r="GD1" s="11"/>
-      <c r="GE1" s="11"/>
-      <c r="GF1" s="11"/>
-      <c r="GG1" s="11"/>
-      <c r="GH1" s="11"/>
-      <c r="GI1" s="11"/>
-      <c r="GJ1" s="11"/>
-      <c r="GK1" s="11"/>
-      <c r="GL1" s="11"/>
-      <c r="GM1" s="11"/>
-      <c r="GN1" s="11"/>
-      <c r="GO1" s="11"/>
-      <c r="GP1" s="11"/>
-      <c r="GQ1" s="11"/>
-      <c r="GR1" s="11"/>
-      <c r="GS1" s="11"/>
-      <c r="GT1" s="11"/>
-      <c r="GU1" s="11"/>
-      <c r="GV1" s="11"/>
-      <c r="GW1" s="11"/>
-      <c r="GX1" s="11"/>
-      <c r="GY1" s="11"/>
-      <c r="GZ1" s="11"/>
-      <c r="HA1" s="11"/>
-      <c r="HB1" s="11"/>
-      <c r="HC1" s="11"/>
-      <c r="HD1" s="11"/>
-      <c r="HE1" s="11"/>
-      <c r="HF1" s="11"/>
-      <c r="HG1" s="11"/>
-      <c r="HH1" s="11"/>
-      <c r="HI1" s="11"/>
-      <c r="HJ1" s="11"/>
-      <c r="HK1" s="11"/>
-      <c r="HL1" s="11"/>
-      <c r="HM1" s="11"/>
-      <c r="HN1" s="11"/>
-      <c r="HO1" s="11"/>
-      <c r="HP1" s="11"/>
-      <c r="HQ1" s="11"/>
-      <c r="HR1" s="11"/>
-      <c r="HS1" s="11"/>
-      <c r="HT1" s="11"/>
-      <c r="HU1" s="11"/>
-      <c r="HV1" s="11"/>
-      <c r="HW1" s="11"/>
-      <c r="HX1" s="11"/>
-      <c r="HY1" s="11"/>
-      <c r="HZ1" s="11"/>
-      <c r="IA1" s="11"/>
-      <c r="IB1" s="11"/>
-      <c r="IC1" s="11"/>
-      <c r="ID1" s="11"/>
-      <c r="IE1" s="11"/>
-      <c r="IF1" s="11"/>
-      <c r="IG1" s="11"/>
-      <c r="IH1" s="11"/>
-      <c r="II1" s="11"/>
-      <c r="IJ1" s="11"/>
-      <c r="IK1" s="11"/>
-      <c r="IL1" s="11"/>
-      <c r="IM1" s="11"/>
-      <c r="IN1" s="11"/>
-      <c r="IO1" s="11"/>
-      <c r="IP1" s="11"/>
-      <c r="IQ1" s="11"/>
-      <c r="IR1" s="11"/>
-      <c r="IS1" s="11"/>
-      <c r="IT1" s="11"/>
-      <c r="IU1" s="12"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
+      <c r="Z1" s="7"/>
+      <c r="AA1" s="7"/>
+      <c r="AB1" s="7"/>
+      <c r="AC1" s="7"/>
+      <c r="AD1" s="7"/>
+      <c r="AE1" s="7"/>
+      <c r="AF1" s="7"/>
+      <c r="AG1" s="7"/>
+      <c r="AH1" s="7"/>
+      <c r="AI1" s="7"/>
+      <c r="AJ1" s="7"/>
+      <c r="AK1" s="7"/>
+      <c r="AL1" s="7"/>
+      <c r="AM1" s="7"/>
+      <c r="AN1" s="7"/>
+      <c r="AO1" s="7"/>
+      <c r="AP1" s="7"/>
+      <c r="AQ1" s="7"/>
+      <c r="AR1" s="7"/>
+      <c r="AS1" s="7"/>
+      <c r="AT1" s="7"/>
+      <c r="AU1" s="7"/>
+      <c r="AV1" s="7"/>
+      <c r="AW1" s="7"/>
+      <c r="AX1" s="7"/>
+      <c r="AY1" s="7"/>
+      <c r="AZ1" s="7"/>
+      <c r="BA1" s="7"/>
+      <c r="BB1" s="7"/>
+      <c r="BC1" s="7"/>
+      <c r="BD1" s="7"/>
+      <c r="BE1" s="7"/>
+      <c r="BF1" s="7"/>
+      <c r="BG1" s="7"/>
+      <c r="BH1" s="7"/>
+      <c r="BI1" s="7"/>
+      <c r="BJ1" s="7"/>
+      <c r="BK1" s="7"/>
+      <c r="BL1" s="7"/>
+      <c r="BM1" s="7"/>
+      <c r="BN1" s="7"/>
+      <c r="BO1" s="7"/>
+      <c r="BP1" s="7"/>
+      <c r="BQ1" s="7"/>
+      <c r="BR1" s="7"/>
+      <c r="BS1" s="7"/>
+      <c r="BT1" s="7"/>
+      <c r="BU1" s="7"/>
+      <c r="BV1" s="7"/>
+      <c r="BW1" s="7"/>
+      <c r="BX1" s="7"/>
+      <c r="BY1" s="7"/>
+      <c r="BZ1" s="7"/>
+      <c r="CA1" s="7"/>
+      <c r="CB1" s="7"/>
+      <c r="CC1" s="7"/>
+      <c r="CD1" s="7"/>
+      <c r="CE1" s="7"/>
+      <c r="CF1" s="7"/>
+      <c r="CG1" s="7"/>
+      <c r="CH1" s="7"/>
+      <c r="CI1" s="7"/>
+      <c r="CJ1" s="7"/>
+      <c r="CK1" s="7"/>
+      <c r="CL1" s="7"/>
+      <c r="CM1" s="7"/>
+      <c r="CN1" s="7"/>
+      <c r="CO1" s="7"/>
+      <c r="CP1" s="7"/>
+      <c r="CQ1" s="7"/>
+      <c r="CR1" s="7"/>
+      <c r="CS1" s="7"/>
+      <c r="CT1" s="7"/>
+      <c r="CU1" s="7"/>
+      <c r="CV1" s="7"/>
+      <c r="CW1" s="7"/>
+      <c r="CX1" s="7"/>
+      <c r="CY1" s="7"/>
+      <c r="CZ1" s="7"/>
+      <c r="DA1" s="7"/>
+      <c r="DB1" s="7"/>
+      <c r="DC1" s="7"/>
+      <c r="DD1" s="7"/>
+      <c r="DE1" s="7"/>
+      <c r="DF1" s="7"/>
+      <c r="DG1" s="7"/>
+      <c r="DH1" s="7"/>
+      <c r="DI1" s="7"/>
+      <c r="DJ1" s="7"/>
+      <c r="DK1" s="7"/>
+      <c r="DL1" s="7"/>
+      <c r="DM1" s="7"/>
+      <c r="DN1" s="7"/>
+      <c r="DO1" s="7"/>
+      <c r="DP1" s="7"/>
+      <c r="DQ1" s="7"/>
+      <c r="DR1" s="7"/>
+      <c r="DS1" s="7"/>
+      <c r="DT1" s="7"/>
+      <c r="DU1" s="7"/>
+      <c r="DV1" s="7"/>
+      <c r="DW1" s="7"/>
+      <c r="DX1" s="7"/>
+      <c r="DY1" s="7"/>
+      <c r="DZ1" s="7"/>
+      <c r="EA1" s="7"/>
+      <c r="EB1" s="7"/>
+      <c r="EC1" s="7"/>
+      <c r="ED1" s="7"/>
+      <c r="EE1" s="7"/>
+      <c r="EF1" s="7"/>
+      <c r="EG1" s="7"/>
+      <c r="EH1" s="7"/>
+      <c r="EI1" s="7"/>
+      <c r="EJ1" s="7"/>
+      <c r="EK1" s="7"/>
+      <c r="EL1" s="7"/>
+      <c r="EM1" s="7"/>
+      <c r="EN1" s="7"/>
+      <c r="EO1" s="7"/>
+      <c r="EP1" s="7"/>
+      <c r="EQ1" s="7"/>
+      <c r="ER1" s="7"/>
+      <c r="ES1" s="7"/>
+      <c r="ET1" s="7"/>
+      <c r="EU1" s="7"/>
+      <c r="EV1" s="7"/>
+      <c r="EW1" s="7"/>
+      <c r="EX1" s="7"/>
+      <c r="EY1" s="7"/>
+      <c r="EZ1" s="7"/>
+      <c r="FA1" s="7"/>
+      <c r="FB1" s="7"/>
+      <c r="FC1" s="7"/>
+      <c r="FD1" s="7"/>
+      <c r="FE1" s="7"/>
+      <c r="FF1" s="7"/>
+      <c r="FG1" s="7"/>
+      <c r="FH1" s="7"/>
+      <c r="FI1" s="7"/>
+      <c r="FJ1" s="7"/>
+      <c r="FK1" s="7"/>
+      <c r="FL1" s="7"/>
+      <c r="FM1" s="7"/>
+      <c r="FN1" s="7"/>
+      <c r="FO1" s="7"/>
+      <c r="FP1" s="7"/>
+      <c r="FQ1" s="7"/>
+      <c r="FR1" s="7"/>
+      <c r="FS1" s="7"/>
+      <c r="FT1" s="7"/>
+      <c r="FU1" s="7"/>
+      <c r="FV1" s="7"/>
+      <c r="FW1" s="7"/>
+      <c r="FX1" s="7"/>
+      <c r="FY1" s="7"/>
+      <c r="FZ1" s="7"/>
+      <c r="GA1" s="7"/>
+      <c r="GB1" s="7"/>
+      <c r="GC1" s="7"/>
+      <c r="GD1" s="7"/>
+      <c r="GE1" s="7"/>
+      <c r="GF1" s="7"/>
+      <c r="GG1" s="7"/>
+      <c r="GH1" s="7"/>
+      <c r="GI1" s="7"/>
+      <c r="GJ1" s="7"/>
+      <c r="GK1" s="7"/>
+      <c r="GL1" s="7"/>
+      <c r="GM1" s="7"/>
+      <c r="GN1" s="7"/>
+      <c r="GO1" s="7"/>
+      <c r="GP1" s="7"/>
+      <c r="GQ1" s="7"/>
+      <c r="GR1" s="7"/>
+      <c r="GS1" s="7"/>
+      <c r="GT1" s="7"/>
+      <c r="GU1" s="7"/>
+      <c r="GV1" s="7"/>
+      <c r="GW1" s="7"/>
+      <c r="GX1" s="7"/>
+      <c r="GY1" s="7"/>
+      <c r="GZ1" s="7"/>
+      <c r="HA1" s="7"/>
+      <c r="HB1" s="7"/>
+      <c r="HC1" s="7"/>
+      <c r="HD1" s="7"/>
+      <c r="HE1" s="7"/>
+      <c r="HF1" s="7"/>
+      <c r="HG1" s="7"/>
+      <c r="HH1" s="7"/>
+      <c r="HI1" s="7"/>
+      <c r="HJ1" s="7"/>
+      <c r="HK1" s="7"/>
+      <c r="HL1" s="7"/>
+      <c r="HM1" s="7"/>
+      <c r="HN1" s="7"/>
+      <c r="HO1" s="7"/>
+      <c r="HP1" s="7"/>
+      <c r="HQ1" s="7"/>
+      <c r="HR1" s="7"/>
+      <c r="HS1" s="7"/>
+      <c r="HT1" s="7"/>
+      <c r="HU1" s="7"/>
+      <c r="HV1" s="7"/>
+      <c r="HW1" s="7"/>
+      <c r="HX1" s="7"/>
+      <c r="HY1" s="7"/>
+      <c r="HZ1" s="7"/>
+      <c r="IA1" s="7"/>
+      <c r="IB1" s="7"/>
+      <c r="IC1" s="7"/>
+      <c r="ID1" s="7"/>
+      <c r="IE1" s="7"/>
+      <c r="IF1" s="7"/>
+      <c r="IG1" s="7"/>
+      <c r="IH1" s="7"/>
+      <c r="II1" s="7"/>
+      <c r="IJ1" s="7"/>
+      <c r="IK1" s="7"/>
+      <c r="IL1" s="7"/>
+      <c r="IM1" s="7"/>
+      <c r="IN1" s="7"/>
+      <c r="IO1" s="7"/>
+      <c r="IP1" s="7"/>
+      <c r="IQ1" s="7"/>
+      <c r="IR1" s="7"/>
+      <c r="IS1" s="7"/>
+      <c r="IT1" s="7"/>
+      <c r="IU1" s="7"/>
+      <c r="IV1" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -2365,25 +1748,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:IR23"/>
-  <sheetFormatPr defaultColWidth="8.85714285714286" defaultRowHeight="12.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="108.714285714286" style="1" customWidth="1"/>
-    <col min="2" max="252" width="8.85714285714286" style="1" customWidth="1"/>
+    <col min="1" max="1" width="108.6640625" style="1" customWidth="1"/>
+    <col min="2" max="252" width="8.83203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.7" customHeight="1" spans="1:1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:252" ht="13.75" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" ht="13.7" customHeight="1" spans="1:1">
-      <c r="A2" s="3"/>
-    </row>
-    <row r="3" ht="15.95" customHeight="1" spans="1:252">
-      <c r="A3" s="4" t="s">
+    <row r="2" spans="1:252" ht="13.75" customHeight="1">
+      <c r="A2" s="10"/>
+    </row>
+    <row r="3" spans="1:252" ht="16" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="IO3"/>
@@ -2391,8 +1773,8 @@
       <c r="IQ3"/>
       <c r="IR3"/>
     </row>
-    <row r="4" ht="15.95" customHeight="1" spans="1:252">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:252" ht="16" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="IO4"/>
@@ -2400,8 +1782,8 @@
       <c r="IQ4"/>
       <c r="IR4"/>
     </row>
-    <row r="5" ht="15.95" customHeight="1" spans="1:252">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:252" ht="16" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="IO5"/>
@@ -2409,8 +1791,8 @@
       <c r="IQ5"/>
       <c r="IR5"/>
     </row>
-    <row r="6" ht="15.95" customHeight="1" spans="1:252">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:252" ht="16" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="IO6"/>
@@ -2418,8 +1800,8 @@
       <c r="IQ6"/>
       <c r="IR6"/>
     </row>
-    <row r="7" ht="15.95" customHeight="1" spans="1:252">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:252" ht="16" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="IO7"/>
@@ -2427,8 +1809,8 @@
       <c r="IQ7"/>
       <c r="IR7"/>
     </row>
-    <row r="8" ht="15.95" customHeight="1" spans="1:252">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:252" ht="16" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="IO8"/>
@@ -2436,8 +1818,8 @@
       <c r="IQ8"/>
       <c r="IR8"/>
     </row>
-    <row r="9" ht="15.95" customHeight="1" spans="1:252">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:252" ht="16" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="IO9"/>
@@ -2445,8 +1827,8 @@
       <c r="IQ9"/>
       <c r="IR9"/>
     </row>
-    <row r="10" ht="15.95" customHeight="1" spans="1:252">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:252" ht="16" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
       <c r="IO10"/>
@@ -2454,68 +1836,68 @@
       <c r="IQ10"/>
       <c r="IR10"/>
     </row>
-    <row r="11" ht="15.95" customHeight="1" spans="1:252">
-      <c r="A11" s="5"/>
+    <row r="11" spans="1:252" ht="16" customHeight="1">
+      <c r="A11" s="3"/>
       <c r="IO11"/>
       <c r="IP11"/>
       <c r="IQ11"/>
       <c r="IR11"/>
     </row>
-    <row r="12" ht="13.7" customHeight="1" spans="1:1">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:252" ht="13.75" customHeight="1">
+      <c r="A12" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" ht="12" customHeight="1" spans="1:1">
-      <c r="A13" s="7"/>
-    </row>
-    <row r="14" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A14" s="8" t="s">
+    <row r="13" spans="1:252" ht="12" customHeight="1">
+      <c r="A13" s="12"/>
+    </row>
+    <row r="14" spans="1:252" ht="16" customHeight="1">
+      <c r="A14" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A15" s="8" t="s">
+    <row r="15" spans="1:252" ht="16" customHeight="1">
+      <c r="A15" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A16" s="8" t="s">
+    <row r="16" spans="1:252" ht="16" customHeight="1">
+      <c r="A16" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A17" s="8" t="s">
+    <row r="17" spans="1:1" ht="16" customHeight="1">
+      <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A18" s="8" t="s">
+    <row r="18" spans="1:1" ht="16" customHeight="1">
+      <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A19" s="8" t="s">
+    <row r="19" spans="1:1" ht="16" customHeight="1">
+      <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A20" s="8" t="s">
+    <row r="20" spans="1:1" ht="16" customHeight="1">
+      <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A21" s="8" t="s">
+    <row r="21" spans="1:1" ht="16" customHeight="1">
+      <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" ht="15.95" customHeight="1" spans="1:1">
-      <c r="A22" s="8" t="s">
+    <row r="22" spans="1:1" ht="16" customHeight="1">
+      <c r="A22" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1" spans="1:1">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:1" ht="13.5" customHeight="1">
+      <c r="A23" s="4" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2524,8 +1906,8 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A12:A13"/>
   </mergeCells>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/src/src/main/webapp/portal/uaa/userAccount/APM_UserAccount_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/APM_UserAccount_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qtang/Desktop/APM/Git/hc-apm-web/src/src/main/webapp/portal/uaa/userAccount/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{98FDF696-3C92-4345-9205-AC46F6727823}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{60CBD4CA-1119-EA49-94F1-71B607D0E8D3}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="28360" windowHeight="10220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>所属集团</t>
   </si>
@@ -126,9 +126,6 @@
   </si>
   <si>
     <t>设备调剂管理人员</t>
-  </si>
-  <si>
-    <t>初始密码</t>
   </si>
 </sst>
 </file>
@@ -1431,7 +1428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IV1"/>
+  <dimension ref="A1:IU1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.33203125" style="1" customWidth="1"/>
@@ -1443,12 +1440,12 @@
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
     <col min="11" max="12" width="8.83203125" style="1" customWidth="1"/>
     <col min="13" max="13" width="24.6640625" style="1" customWidth="1"/>
-    <col min="14" max="15" width="30" style="1" customWidth="1"/>
-    <col min="16" max="16" width="32.6640625" style="1" customWidth="1"/>
-    <col min="17" max="256" width="8.83203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="30" style="1" customWidth="1"/>
+    <col min="15" max="15" width="32.6640625" style="1" customWidth="1"/>
+    <col min="16" max="255" width="8.83203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:256" ht="30.75" customHeight="1">
+    <row r="1" spans="1:255" ht="30.75" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1492,12 +1489,10 @@
         <v>13</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
       <c r="S1" s="7"/>
       <c r="T1" s="7"/>
@@ -1735,8 +1730,7 @@
       <c r="IR1" s="7"/>
       <c r="IS1" s="7"/>
       <c r="IT1" s="7"/>
-      <c r="IU1" s="7"/>
-      <c r="IV1" s="8"/>
+      <c r="IU1" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/src/main/webapp/portal/uaa/userAccount/APM_UserAccount_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/APM_UserAccount_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10610"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qtang/Desktop/APM/Git/hc-apm-web/src/src/main/webapp/portal/uaa/userAccount/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212670825\Desktop\APM\Git\hc-apm-web\src\src\main\webapp\portal\uaa\userAccount\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{60CBD4CA-1119-EA49-94F1-71B607D0E8D3}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4513D781-2EE6-4F0A-B374-E210E144F0F7}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="28360" windowHeight="10220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>所属集团</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>设备调剂管理人员</t>
+  </si>
+  <si>
+    <t>职务</t>
   </si>
 </sst>
 </file>
@@ -1428,24 +1431,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IU1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12.75" customHeight="1"/>
+  <dimension ref="A1:IV1"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="13.5" style="1" customWidth="1"/>
+    <col min="3" max="4" width="13.44140625" style="1" customWidth="1"/>
     <col min="5" max="6" width="14.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.83203125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.77734375" style="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
-    <col min="11" max="12" width="8.83203125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.77734375" style="1" customWidth="1"/>
     <col min="13" max="13" width="24.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="30" style="1" customWidth="1"/>
-    <col min="15" max="15" width="32.6640625" style="1" customWidth="1"/>
-    <col min="16" max="255" width="8.83203125" style="1" customWidth="1"/>
+    <col min="14" max="15" width="30" style="1" customWidth="1"/>
+    <col min="16" max="16" width="32.6640625" style="1" customWidth="1"/>
+    <col min="17" max="256" width="8.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:255" ht="30.75" customHeight="1">
+    <row r="1" spans="1:256" ht="30.75" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1489,10 +1492,12 @@
         <v>13</v>
       </c>
       <c r="O1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="7"/>
+      <c r="Q1" s="6"/>
       <c r="R1" s="7"/>
       <c r="S1" s="7"/>
       <c r="T1" s="7"/>
@@ -1730,7 +1735,8 @@
       <c r="IR1" s="7"/>
       <c r="IS1" s="7"/>
       <c r="IT1" s="7"/>
-      <c r="IU1" s="8"/>
+      <c r="IU1" s="7"/>
+      <c r="IV1" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1744,21 +1750,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:IR23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="108.6640625" style="1" customWidth="1"/>
-    <col min="2" max="252" width="8.83203125" style="1" customWidth="1"/>
+    <col min="2" max="252" width="8.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:252" ht="13.75" customHeight="1">
+    <row r="1" spans="1:252" ht="13.8" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:252" ht="13.75" customHeight="1">
+    <row r="2" spans="1:252" ht="13.8" customHeight="1">
       <c r="A2" s="10"/>
     </row>
-    <row r="3" spans="1:252" ht="16" customHeight="1">
+    <row r="3" spans="1:252" ht="16.05" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
@@ -1767,7 +1773,7 @@
       <c r="IQ3"/>
       <c r="IR3"/>
     </row>
-    <row r="4" spans="1:252" ht="16" customHeight="1">
+    <row r="4" spans="1:252" ht="16.05" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -1776,7 +1782,7 @@
       <c r="IQ4"/>
       <c r="IR4"/>
     </row>
-    <row r="5" spans="1:252" ht="16" customHeight="1">
+    <row r="5" spans="1:252" ht="16.05" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
@@ -1785,7 +1791,7 @@
       <c r="IQ5"/>
       <c r="IR5"/>
     </row>
-    <row r="6" spans="1:252" ht="16" customHeight="1">
+    <row r="6" spans="1:252" ht="16.05" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -1794,7 +1800,7 @@
       <c r="IQ6"/>
       <c r="IR6"/>
     </row>
-    <row r="7" spans="1:252" ht="16" customHeight="1">
+    <row r="7" spans="1:252" ht="16.05" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -1803,7 +1809,7 @@
       <c r="IQ7"/>
       <c r="IR7"/>
     </row>
-    <row r="8" spans="1:252" ht="16" customHeight="1">
+    <row r="8" spans="1:252" ht="16.05" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -1812,7 +1818,7 @@
       <c r="IQ8"/>
       <c r="IR8"/>
     </row>
-    <row r="9" spans="1:252" ht="16" customHeight="1">
+    <row r="9" spans="1:252" ht="16.05" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1821,7 +1827,7 @@
       <c r="IQ9"/>
       <c r="IR9"/>
     </row>
-    <row r="10" spans="1:252" ht="16" customHeight="1">
+    <row r="10" spans="1:252" ht="16.05" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
@@ -1830,14 +1836,14 @@
       <c r="IQ10"/>
       <c r="IR10"/>
     </row>
-    <row r="11" spans="1:252" ht="16" customHeight="1">
+    <row r="11" spans="1:252" ht="16.05" customHeight="1">
       <c r="A11" s="3"/>
       <c r="IO11"/>
       <c r="IP11"/>
       <c r="IQ11"/>
       <c r="IR11"/>
     </row>
-    <row r="12" spans="1:252" ht="13.75" customHeight="1">
+    <row r="12" spans="1:252" ht="13.8" customHeight="1">
       <c r="A12" s="11" t="s">
         <v>24</v>
       </c>
@@ -1845,47 +1851,47 @@
     <row r="13" spans="1:252" ht="12" customHeight="1">
       <c r="A13" s="12"/>
     </row>
-    <row r="14" spans="1:252" ht="16" customHeight="1">
+    <row r="14" spans="1:252" ht="16.05" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:252" ht="16" customHeight="1">
+    <row r="15" spans="1:252" ht="16.05" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:252" ht="16" customHeight="1">
+    <row r="16" spans="1:252" ht="16.05" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="16" customHeight="1">
+    <row r="17" spans="1:1" ht="16.05" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="16" customHeight="1">
+    <row r="18" spans="1:1" ht="16.05" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="16" customHeight="1">
+    <row r="19" spans="1:1" ht="16.05" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="16" customHeight="1">
+    <row r="20" spans="1:1" ht="16.05" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="16" customHeight="1">
+    <row r="21" spans="1:1" ht="16.05" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="16" customHeight="1">
+    <row r="22" spans="1:1" ht="16.05" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>33</v>
       </c>

--- a/src/src/main/webapp/portal/uaa/userAccount/APM_UserAccount_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/APM_UserAccount_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212670825\Desktop\APM\Git\hc-apm-web\src\src\main\webapp\portal\uaa\userAccount\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4513D781-2EE6-4F0A-B374-E210E144F0F7}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631C3C51-5F29-46C5-8817-9DA1B8C9738B}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>所属集团</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>职务</t>
+  </si>
+  <si>
+    <t>标签</t>
   </si>
 </sst>
 </file>
@@ -1431,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IV1"/>
+  <dimension ref="A1:IW1"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.33203125" style="1" customWidth="1"/>
@@ -1443,12 +1446,12 @@
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
     <col min="11" max="12" width="8.77734375" style="1" customWidth="1"/>
     <col min="13" max="13" width="24.6640625" style="1" customWidth="1"/>
-    <col min="14" max="15" width="30" style="1" customWidth="1"/>
-    <col min="16" max="16" width="32.6640625" style="1" customWidth="1"/>
-    <col min="17" max="256" width="8.77734375" style="1" customWidth="1"/>
+    <col min="14" max="16" width="30" style="1" customWidth="1"/>
+    <col min="17" max="17" width="32.6640625" style="1" customWidth="1"/>
+    <col min="18" max="257" width="8.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:256" ht="30.75" customHeight="1">
+    <row r="1" spans="1:257" ht="30.75" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1495,10 +1498,12 @@
         <v>35</v>
       </c>
       <c r="P1" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="7"/>
+      <c r="R1" s="6"/>
       <c r="S1" s="7"/>
       <c r="T1" s="7"/>
       <c r="U1" s="7"/>
@@ -1736,7 +1741,8 @@
       <c r="IS1" s="7"/>
       <c r="IT1" s="7"/>
       <c r="IU1" s="7"/>
-      <c r="IV1" s="8"/>
+      <c r="IV1" s="7"/>
+      <c r="IW1" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/src/main/webapp/portal/uaa/userAccount/APM_UserAccount_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/APM_UserAccount_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212670825\Desktop\APM\Git\hc-apm-web\src\src\main\webapp\portal\uaa\userAccount\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503310146\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631C3C51-5F29-46C5-8817-9DA1B8C9738B}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2EC0A0F-83B9-49E0-B08C-F864A31C0717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>所属集团</t>
   </si>
@@ -132,13 +132,17 @@
   </si>
   <si>
     <t>标签</t>
+  </si>
+  <si>
+    <t>停用?*</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -149,13 +153,20 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -312,7 +323,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
@@ -1434,24 +1445,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IW1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.75" customHeight="1"/>
+  <dimension ref="A1:IX1"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="13.44140625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="14.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.77734375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="13.42578125" style="1" customWidth="1"/>
+    <col min="5" max="6" width="14.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
-    <col min="11" max="12" width="8.77734375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="24.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16" width="30" style="1" customWidth="1"/>
-    <col min="17" max="17" width="32.6640625" style="1" customWidth="1"/>
-    <col min="18" max="257" width="8.77734375" style="1" customWidth="1"/>
+    <col min="11" max="13" width="8.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="24.7109375" style="1" customWidth="1"/>
+    <col min="15" max="17" width="30" style="1" customWidth="1"/>
+    <col min="18" max="18" width="32.7109375" style="1" customWidth="1"/>
+    <col min="19" max="258" width="8.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:257" ht="30.75" customHeight="1">
+    <row r="1" spans="1:258" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1489,22 +1500,24 @@
         <v>11</v>
       </c>
       <c r="M1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="6"/>
-      <c r="S1" s="7"/>
+      <c r="S1" s="6"/>
       <c r="T1" s="7"/>
       <c r="U1" s="7"/>
       <c r="V1" s="7"/>
@@ -1742,9 +1755,11 @@
       <c r="IT1" s="7"/>
       <c r="IU1" s="7"/>
       <c r="IV1" s="7"/>
-      <c r="IW1" s="8"/>
+      <c r="IW1" s="7"/>
+      <c r="IX1" s="8"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>
@@ -1756,21 +1771,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:IR23"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="108.6640625" style="1" customWidth="1"/>
-    <col min="2" max="252" width="8.77734375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="108.7109375" style="1" customWidth="1"/>
+    <col min="2" max="252" width="8.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:252" ht="13.8" customHeight="1">
+    <row r="1" spans="1:252" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:252" ht="13.8" customHeight="1">
+    <row r="2" spans="1:252" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10"/>
     </row>
-    <row r="3" spans="1:252" ht="16.05" customHeight="1">
+    <row r="3" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
@@ -1779,7 +1794,7 @@
       <c r="IQ3"/>
       <c r="IR3"/>
     </row>
-    <row r="4" spans="1:252" ht="16.05" customHeight="1">
+    <row r="4" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -1788,7 +1803,7 @@
       <c r="IQ4"/>
       <c r="IR4"/>
     </row>
-    <row r="5" spans="1:252" ht="16.05" customHeight="1">
+    <row r="5" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
@@ -1797,7 +1812,7 @@
       <c r="IQ5"/>
       <c r="IR5"/>
     </row>
-    <row r="6" spans="1:252" ht="16.05" customHeight="1">
+    <row r="6" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -1806,7 +1821,7 @@
       <c r="IQ6"/>
       <c r="IR6"/>
     </row>
-    <row r="7" spans="1:252" ht="16.05" customHeight="1">
+    <row r="7" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -1815,7 +1830,7 @@
       <c r="IQ7"/>
       <c r="IR7"/>
     </row>
-    <row r="8" spans="1:252" ht="16.05" customHeight="1">
+    <row r="8" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -1824,7 +1839,7 @@
       <c r="IQ8"/>
       <c r="IR8"/>
     </row>
-    <row r="9" spans="1:252" ht="16.05" customHeight="1">
+    <row r="9" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1833,7 +1848,7 @@
       <c r="IQ9"/>
       <c r="IR9"/>
     </row>
-    <row r="10" spans="1:252" ht="16.05" customHeight="1">
+    <row r="10" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
@@ -1842,67 +1857,67 @@
       <c r="IQ10"/>
       <c r="IR10"/>
     </row>
-    <row r="11" spans="1:252" ht="16.05" customHeight="1">
+    <row r="11" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
       <c r="IO11"/>
       <c r="IP11"/>
       <c r="IQ11"/>
       <c r="IR11"/>
     </row>
-    <row r="12" spans="1:252" ht="13.8" customHeight="1">
+    <row r="12" spans="1:252" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:252" ht="12" customHeight="1">
+    <row r="13" spans="1:252" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12"/>
     </row>
-    <row r="14" spans="1:252" ht="16.05" customHeight="1">
+    <row r="14" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:252" ht="16.05" customHeight="1">
+    <row r="15" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:252" ht="16.05" customHeight="1">
+    <row r="16" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="16.05" customHeight="1">
+    <row r="17" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="16.05" customHeight="1">
+    <row r="18" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="16.05" customHeight="1">
+    <row r="19" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="16.05" customHeight="1">
+    <row r="20" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="16.05" customHeight="1">
+    <row r="21" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="16.05" customHeight="1">
+    <row r="22" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="13.5" customHeight="1">
+    <row r="23" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>34</v>
       </c>
@@ -1912,8 +1927,9 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A12:A13"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/src/src/main/webapp/portal/uaa/userAccount/APM_UserAccount_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/userAccount/APM_UserAccount_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503310146\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503282840\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2EC0A0F-83B9-49E0-B08C-F864A31C0717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC848C27-0C1A-4BB8-BB8D-EAAE75C9E79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6630" yWindow="6420" windowWidth="21390" windowHeight="12090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>所属集团</t>
   </si>
@@ -136,13 +136,16 @@
   <si>
     <t>停用?*</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产分类</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -1445,8 +1448,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IX1"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:IY1"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
@@ -1457,12 +1460,12 @@
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
     <col min="11" max="13" width="8.7109375" style="1" customWidth="1"/>
     <col min="14" max="14" width="24.7109375" style="1" customWidth="1"/>
-    <col min="15" max="17" width="30" style="1" customWidth="1"/>
-    <col min="18" max="18" width="32.7109375" style="1" customWidth="1"/>
-    <col min="19" max="258" width="8.7109375" style="1" customWidth="1"/>
+    <col min="15" max="18" width="30" style="1" customWidth="1"/>
+    <col min="19" max="19" width="32.7109375" style="1" customWidth="1"/>
+    <col min="20" max="259" width="8.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:258" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:259" ht="30.75" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1515,10 +1518,12 @@
         <v>36</v>
       </c>
       <c r="R1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="6"/>
-      <c r="T1" s="7"/>
+      <c r="T1" s="6"/>
       <c r="U1" s="7"/>
       <c r="V1" s="7"/>
       <c r="W1" s="7"/>
@@ -1756,7 +1761,8 @@
       <c r="IU1" s="7"/>
       <c r="IV1" s="7"/>
       <c r="IW1" s="7"/>
-      <c r="IX1" s="8"/>
+      <c r="IX1" s="7"/>
+      <c r="IY1" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1771,21 +1777,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:IR23"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="108.7109375" style="1" customWidth="1"/>
     <col min="2" max="252" width="8.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:252" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:252" ht="13.9" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:252" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:252" ht="13.9" customHeight="1">
       <c r="A2" s="10"/>
     </row>
-    <row r="3" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:252" ht="16.149999999999999" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
@@ -1794,7 +1800,7 @@
       <c r="IQ3"/>
       <c r="IR3"/>
     </row>
-    <row r="4" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:252" ht="16.149999999999999" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -1803,7 +1809,7 @@
       <c r="IQ4"/>
       <c r="IR4"/>
     </row>
-    <row r="5" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:252" ht="16.149999999999999" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
@@ -1812,7 +1818,7 @@
       <c r="IQ5"/>
       <c r="IR5"/>
     </row>
-    <row r="6" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:252" ht="16.149999999999999" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -1821,7 +1827,7 @@
       <c r="IQ6"/>
       <c r="IR6"/>
     </row>
-    <row r="7" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:252" ht="16.149999999999999" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -1830,7 +1836,7 @@
       <c r="IQ7"/>
       <c r="IR7"/>
     </row>
-    <row r="8" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:252" ht="16.149999999999999" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -1839,7 +1845,7 @@
       <c r="IQ8"/>
       <c r="IR8"/>
     </row>
-    <row r="9" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:252" ht="16.149999999999999" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1848,7 +1854,7 @@
       <c r="IQ9"/>
       <c r="IR9"/>
     </row>
-    <row r="10" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:252" ht="16.149999999999999" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
@@ -1857,67 +1863,67 @@
       <c r="IQ10"/>
       <c r="IR10"/>
     </row>
-    <row r="11" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:252" ht="16.149999999999999" customHeight="1">
       <c r="A11" s="3"/>
       <c r="IO11"/>
       <c r="IP11"/>
       <c r="IQ11"/>
       <c r="IR11"/>
     </row>
-    <row r="12" spans="1:252" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:252" ht="13.9" customHeight="1">
       <c r="A12" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:252" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:252" ht="12" customHeight="1">
       <c r="A13" s="12"/>
     </row>
-    <row r="14" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:252" ht="16.149999999999999" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:252" ht="16.149999999999999" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:252" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:252" ht="16.149999999999999" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" ht="13.5" customHeight="1">
       <c r="A23" s="4" t="s">
         <v>34</v>
       </c>
